--- a/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Triphammer_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Triphammer_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,552 @@
         <v>50.79</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4455234</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Artichoke Hrt Qtrd</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="E24" t="n">
+        <v>45.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2477933</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bacon (Pre-Cooked)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>511.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0490508</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Brie</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="E26" t="n">
+        <v>53.88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7058803</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Can - Tomato - Whole Peeled</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="E27" t="n">
+        <v>117.93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7206874</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Can - Tomato (Crushed)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="E28" t="n">
+        <v>130.64</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4052171</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Apple Red - Fresh</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="E29" t="n">
+        <v>27.08</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>9546982</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arugula - Fresh</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="E30" t="n">
+        <v>61.05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2326429</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Broccoli Floret - Fresh</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>59.54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>9074360</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pepper - Yellow Bell</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="E32" t="n">
+        <v>32.89</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2006567</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Potato - Chef</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7489339</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Garlic - Fresh (Peeled)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>70.08</v>
+      </c>
+      <c r="E34" t="n">
+        <v>70.08</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1028519</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tomato - Fresh Sliced</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="E35" t="n">
+        <v>185.28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9047468</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Egg Patty</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="E36" t="n">
+        <v>363.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4886244</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Goat Cheese</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="E37" t="n">
+        <v>46.44</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8457368</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Oil - Corn</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="E38" t="n">
+        <v>102.96</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7520950</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Can - Pizza Sauce</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="E39" t="n">
+        <v>41.22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1027629</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cheddar - (Sliced)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="E40" t="n">
+        <v>279.28</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1035842</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Feta - Pail</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="E41" t="n">
+        <v>92.87</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6318732</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FRZ Fruit - Apple (Sliced)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="E42" t="n">
+        <v>54.91</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7722184</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Parmesan (Grated)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="E43" t="n">
+        <v>59.95</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6432884</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pepper Jack (Sliced)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="E44" t="n">
+        <v>84.66</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1028165</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pickle - Dill Chip</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="E45" t="n">
+        <v>34.09</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1028188</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tortellini - Cheese</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="E46" t="n">
+        <v>32.22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8255796</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tuna White Chunk (Pouch)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>72</v>
+      </c>
+      <c r="E47" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6364494</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Yogurt - Greek (Bulk)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="E48" t="n">
+        <v>26.96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4890026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Yogurt - Plain (BIB)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="E49" t="n">
+        <v>174.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
